--- a/release_forms/004_covid_19_questionnaire_and_release_form--release_forms.xlsx
+++ b/release_forms/004_covid_19_questionnaire_and_release_form--release_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'hypertension'}</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Hypertension'}</t>
+          <t>Hypertension</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'high_cholesterol'}</t>
+          <t>high_cholesterol</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'High Cholesterol'}</t>
+          <t>High Cholesterol</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'peanut'}</t>
+          <t>peanut</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Peanut'}</t>
+          <t>Peanut</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'gluten'}</t>
+          <t>gluten</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Gluten'}</t>
+          <t>Gluten</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
